--- a/Slanger_hylser.xlsx
+++ b/Slanger_hylser.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\slangeprogram_v18\_internal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\script_2\nuitka\my_slangeprogram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE94980-1361-46D1-96D0-56BADE5DBA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3D37D3-2455-4B81-94AC-3C14D4E740CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B701A88-204F-43FD-9B11-C042844D6F26}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{7B701A88-204F-43FD-9B11-C042844D6F26}"/>
   </bookViews>
   <sheets>
     <sheet name="Slange+Hylse" sheetId="1" r:id="rId1"/>
     <sheet name="MONT" sheetId="4" r:id="rId2"/>
     <sheet name="Trykktest" sheetId="5" r:id="rId3"/>
     <sheet name="Prikling" sheetId="6" r:id="rId4"/>
+    <sheet name="ABS Sert." sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="352">
   <si>
     <t>ProV-10 5/8" Bruk Pro2T</t>
   </si>
@@ -1086,6 +1087,15 @@
   </si>
   <si>
     <t>Kolonne1</t>
+  </si>
+  <si>
+    <t>ABS</t>
+  </si>
+  <si>
+    <t>Type Approval1</t>
+  </si>
+  <si>
+    <t>ABS Sertifisering/Bevitnelse</t>
   </si>
 </sst>
 </file>
@@ -1236,7 +1246,45 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="23">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
     <dxf>
       <border outline="0">
         <top style="thin">
@@ -1573,31 +1621,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{13F7CE61-B835-454D-AFC3-CEB551034587}" name="Tabell2" displayName="Tabell2" ref="A1:L121" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18">
-  <autoFilter ref="A1:L121" xr:uid="{13F7CE61-B835-454D-AFC3-CEB551034587}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{13F7CE61-B835-454D-AFC3-CEB551034587}" name="Tabell2" displayName="Tabell2" ref="A1:M121" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21">
+  <autoFilter ref="A1:M121" xr:uid="{13F7CE61-B835-454D-AFC3-CEB551034587}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H117">
     <sortCondition ref="B1:B117"/>
   </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{251763FC-B91D-4A89-B8B7-24A309DCF786}" name="Prod.no" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{6F1BDC04-FAD1-44CE-988A-F11C7CD266F7}" name="Beskrivelse" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{6C6D1FB6-7476-4DFA-9F05-D4D8C95C03BB}" name="Trykk(bar)" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{320FBDDA-F2D6-4BC8-8BC6-EFEA77CEB457}" name="Stål hylse(Posd.no)" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{132BF19B-0DFE-4C8D-85C6-693B0B60662C}" name="Stål hylse(beskrivelse)" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{C92843E4-878E-4C75-8377-AFF9EEC911E7}" name="316 hylse(Posd.no)" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{08D3EFC1-C39C-4CE2-A7AC-FB42CCC5D810}" name="316 hylse(beskrivelse)" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{E6D17188-97DD-4D95-A901-3FD70A9FCA0A}" name="Dimensjon" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{56F2FEA3-E0B4-4E55-964E-D824A8370847}" name="Beskrivelse_2" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{3F602BE4-7A8F-4F61-BED5-79A8D52CC744}" name="Type Approval" dataDxfId="8"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{251763FC-B91D-4A89-B8B7-24A309DCF786}" name="Prod.no" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{6F1BDC04-FAD1-44CE-988A-F11C7CD266F7}" name="Beskrivelse" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{6C6D1FB6-7476-4DFA-9F05-D4D8C95C03BB}" name="Trykk(bar)" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{320FBDDA-F2D6-4BC8-8BC6-EFEA77CEB457}" name="Stål hylse(Posd.no)" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{132BF19B-0DFE-4C8D-85C6-693B0B60662C}" name="Stål hylse(beskrivelse)" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{C92843E4-878E-4C75-8377-AFF9EEC911E7}" name="316 hylse(Posd.no)" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{08D3EFC1-C39C-4CE2-A7AC-FB42CCC5D810}" name="316 hylse(beskrivelse)" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{E6D17188-97DD-4D95-A901-3FD70A9FCA0A}" name="Dimensjon" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{56F2FEA3-E0B4-4E55-964E-D824A8370847}" name="Beskrivelse_2" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{3F602BE4-7A8F-4F61-BED5-79A8D52CC744}" name="Type Approval" dataDxfId="11"/>
     <tableColumn id="11" xr3:uid="{87DF9766-F9A2-4EE1-82F9-950B951AB038}" name="produsent"/>
     <tableColumn id="12" xr3:uid="{C2EE9A93-1E62-4D6D-B9A5-962480D9AE7C}" name="Kolonne1"/>
+    <tableColumn id="13" xr3:uid="{4D008D02-01AE-4A0B-A561-8C5593D5372F}" name="Type Approval1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6BEF41EF-32DD-420C-B223-1654EADDF20B}" name="Tabell3" displayName="Tabell3" ref="A1:B5" totalsRowShown="0" headerRowDxfId="7" tableBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6BEF41EF-32DD-420C-B223-1654EADDF20B}" name="Tabell3" displayName="Tabell3" ref="A1:B5" totalsRowShown="0" headerRowDxfId="10" tableBorderDxfId="9">
   <autoFilter ref="A1:B5" xr:uid="{6BEF41EF-32DD-420C-B223-1654EADDF20B}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{124E6E90-798A-432B-86E3-10556B79F89A}" name="Prod.no"/>
@@ -1608,7 +1657,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7DBC489E-59EF-4879-9FE4-76393ACAC418}" name="Tabell6" displayName="Tabell6" ref="A1:B10" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7DBC489E-59EF-4879-9FE4-76393ACAC418}" name="Tabell6" displayName="Tabell6" ref="A1:B10" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="A1:B10" xr:uid="{7DBC489E-59EF-4879-9FE4-76393ACAC418}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B10">
     <sortCondition ref="A1:A10"/>
@@ -1622,11 +1671,22 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3CAE563-162D-4C3A-BEDE-177DC1706CEB}" name="Tabell1" displayName="Tabell1" ref="A1:B4" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3CAE563-162D-4C3A-BEDE-177DC1706CEB}" name="Tabell1" displayName="Tabell1" ref="A1:B4" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
   <autoFilter ref="A1:B4" xr:uid="{A3CAE563-162D-4C3A-BEDE-177DC1706CEB}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{35D6F108-6881-4EB0-9336-2AB6B9CC07A8}" name="Prod.no"/>
     <tableColumn id="2" xr3:uid="{2E322078-9A9A-4252-9CBE-EC01E15A5F2A}" name="Beskrivelse"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AD8EAC2D-367A-4714-BC50-04B242895EDA}" name="Tabell4" displayName="Tabell4" ref="A1:B2" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+  <autoFilter ref="A1:B2" xr:uid="{AD8EAC2D-367A-4714-BC50-04B242895EDA}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{ECAA00E3-7280-4EA3-8067-7B2E7B36DD00}" name="Prod.no"/>
+    <tableColumn id="2" xr3:uid="{4E35FD51-CBD8-4747-8C56-419ECA215C8E}" name="Beskrivelse"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1949,7 +2009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C23720-E2F4-4ED2-AFFB-B898F6C06039}">
-  <dimension ref="A1:L121"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="57.7109375" bestFit="1" customWidth="1"/>
@@ -1960,9 +2020,10 @@
     <col min="7" max="7" width="51.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="56.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -1999,8 +2060,11 @@
       <c r="L1" s="7" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" s="7" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>27056</v>
       </c>
@@ -2030,7 +2094,7 @@
       </c>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>27059</v>
       </c>
@@ -2060,7 +2124,7 @@
       </c>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>25104</v>
       </c>
@@ -2090,7 +2154,7 @@
       </c>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>25064</v>
       </c>
@@ -2122,7 +2186,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>25105</v>
       </c>
@@ -2152,7 +2216,7 @@
       </c>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>25073</v>
       </c>
@@ -2184,7 +2248,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>25106</v>
       </c>
@@ -2214,7 +2278,7 @@
       </c>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>27060</v>
       </c>
@@ -2246,7 +2310,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>25107</v>
       </c>
@@ -2276,7 +2340,7 @@
       </c>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>27063</v>
       </c>
@@ -2308,7 +2372,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>25108</v>
       </c>
@@ -2338,7 +2402,7 @@
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>27061</v>
       </c>
@@ -2370,7 +2434,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>25101</v>
       </c>
@@ -2400,7 +2464,7 @@
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>27065</v>
       </c>
@@ -2432,7 +2496,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>25111</v>
       </c>
@@ -2462,7 +2526,7 @@
       </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>25109</v>
       </c>
@@ -2493,8 +2557,11 @@
       <c r="J17" s="1" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M17" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>25527</v>
       </c>
@@ -2525,8 +2592,11 @@
       <c r="J18" s="1" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M18" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>25550</v>
       </c>
@@ -2557,8 +2627,11 @@
       <c r="J19" s="1" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M19" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>25585</v>
       </c>
@@ -2589,8 +2662,11 @@
       <c r="J20" s="1" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M20" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>25517</v>
       </c>
@@ -2621,8 +2697,11 @@
       <c r="J21" s="1" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M21" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>25529</v>
       </c>
@@ -2653,8 +2732,11 @@
       <c r="J22" s="1" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M22" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>25175</v>
       </c>
@@ -2685,8 +2767,11 @@
       <c r="J23" s="1" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M23" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>25530</v>
       </c>
@@ -2717,8 +2802,11 @@
       <c r="J24" s="1" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M24" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>25176</v>
       </c>
@@ -2749,8 +2837,11 @@
       <c r="J25" s="1" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M25" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25501</v>
       </c>
@@ -2780,7 +2871,7 @@
       </c>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25502</v>
       </c>
@@ -2812,7 +2903,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>25503</v>
       </c>
@@ -2844,7 +2935,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>25623</v>
       </c>
@@ -2876,7 +2967,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>25504</v>
       </c>
@@ -2908,7 +2999,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>25505</v>
       </c>
@@ -2940,7 +3031,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>25506</v>
       </c>
@@ -2972,7 +3063,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>26851</v>
       </c>
@@ -3006,8 +3097,11 @@
       <c r="K33" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M33" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>26852</v>
       </c>
@@ -3041,8 +3135,11 @@
       <c r="K34" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M34" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>26853</v>
       </c>
@@ -3076,8 +3173,11 @@
       <c r="K35" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M35" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>26854</v>
       </c>
@@ -3111,8 +3211,11 @@
       <c r="K36" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M36" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>26855</v>
       </c>
@@ -3146,8 +3249,11 @@
       <c r="K37" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M37" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>26856</v>
       </c>
@@ -3181,8 +3287,11 @@
       <c r="K38" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M38" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>26857</v>
       </c>
@@ -3216,8 +3325,11 @@
       <c r="K39" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M39" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>26858</v>
       </c>
@@ -3251,8 +3363,11 @@
       <c r="K40" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M40" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>26859</v>
       </c>
@@ -3286,8 +3401,11 @@
       <c r="K41" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M41" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>26774</v>
       </c>
@@ -3318,8 +3436,11 @@
       <c r="J42" s="1" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M42" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>26844</v>
       </c>
@@ -3350,8 +3471,11 @@
       <c r="J43" s="1" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M43" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>26784</v>
       </c>
@@ -3382,8 +3506,11 @@
       <c r="J44" s="1" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M44" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>26787</v>
       </c>
@@ -3414,8 +3541,11 @@
       <c r="J45" s="1" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M45" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>26798</v>
       </c>
@@ -3446,8 +3576,11 @@
       <c r="J46" s="1" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M46" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>26799</v>
       </c>
@@ -3481,8 +3614,11 @@
       <c r="L47">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M47" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>26809</v>
       </c>
@@ -3516,8 +3652,11 @@
       <c r="L48">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M48" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>26810</v>
       </c>
@@ -3551,8 +3690,11 @@
       <c r="L49">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M49" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>26814</v>
       </c>
@@ -3582,8 +3724,11 @@
       <c r="L50">
         <v>5</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M50" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>26818</v>
       </c>
@@ -3613,8 +3758,11 @@
       <c r="L51">
         <v>5</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M51" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>26827</v>
       </c>
@@ -3648,8 +3796,11 @@
       <c r="L52">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M52" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>26831</v>
       </c>
@@ -3683,8 +3834,11 @@
       <c r="L53">
         <v>5</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M53" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>26835</v>
       </c>
@@ -3718,8 +3872,11 @@
       <c r="L54">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M54" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>26838</v>
       </c>
@@ -3753,8 +3910,11 @@
       <c r="L55">
         <v>5</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M55" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>26841</v>
       </c>
@@ -3788,8 +3948,11 @@
       <c r="L56">
         <v>5</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M56" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>26548</v>
       </c>
@@ -3823,8 +3986,11 @@
       <c r="K57" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M57" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>27008</v>
       </c>
@@ -3858,8 +4024,11 @@
       <c r="K58" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M58" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>27009</v>
       </c>
@@ -3893,8 +4062,11 @@
       <c r="K59" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M59" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>25619</v>
       </c>
@@ -3928,8 +4100,11 @@
       <c r="K60" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M60" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>27043</v>
       </c>
@@ -3963,8 +4138,11 @@
       <c r="K61" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M61" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>26549</v>
       </c>
@@ -3998,8 +4176,11 @@
       <c r="K62" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M62" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>26860</v>
       </c>
@@ -4033,8 +4214,11 @@
       <c r="K63" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M63" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>26861</v>
       </c>
@@ -4068,8 +4252,11 @@
       <c r="K64" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M64" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>26864</v>
       </c>
@@ -4103,8 +4290,11 @@
       <c r="K65" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M65" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>26865</v>
       </c>
@@ -4138,8 +4328,11 @@
       <c r="K66" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M66" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>26866</v>
       </c>
@@ -4173,8 +4366,11 @@
       <c r="K67" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M67" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>26867</v>
       </c>
@@ -4208,8 +4404,11 @@
       <c r="K68" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M68" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>26868</v>
       </c>
@@ -4243,8 +4442,11 @@
       <c r="K69" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M69" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>58850</v>
       </c>
@@ -4278,8 +4480,11 @@
       <c r="K70" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M70" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>26870</v>
       </c>
@@ -4313,8 +4518,11 @@
       <c r="K71" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M71" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>26869</v>
       </c>
@@ -4348,8 +4556,11 @@
       <c r="K72" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M72" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>25637</v>
       </c>
@@ -4383,8 +4594,11 @@
       <c r="K73" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M73" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>26871</v>
       </c>
@@ -4418,8 +4632,11 @@
       <c r="K74" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M74" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>25621</v>
       </c>
@@ -4453,8 +4670,11 @@
       <c r="K75" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M75" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>25065</v>
       </c>
@@ -4488,8 +4708,11 @@
       <c r="K76" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M76" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>25624</v>
       </c>
@@ -4523,8 +4746,11 @@
       <c r="K77" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M77" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>25066</v>
       </c>
@@ -4558,8 +4784,11 @@
       <c r="K78" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M78" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>25651</v>
       </c>
@@ -4593,8 +4822,11 @@
       <c r="K79" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M79" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>25068</v>
       </c>
@@ -4628,8 +4860,11 @@
       <c r="K80" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M80" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>26872</v>
       </c>
@@ -4663,8 +4898,11 @@
       <c r="K81" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M81" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>26873</v>
       </c>
@@ -4698,8 +4936,11 @@
       <c r="K82" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M82" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>25636</v>
       </c>
@@ -4733,8 +4974,11 @@
       <c r="K83" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M83" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>26874</v>
       </c>
@@ -4768,8 +5012,11 @@
       <c r="K84" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M84" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>25102</v>
       </c>
@@ -4803,8 +5050,11 @@
       <c r="K85" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M85" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>27052</v>
       </c>
@@ -4838,8 +5088,11 @@
       <c r="K86" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M86" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>26876</v>
       </c>
@@ -4873,8 +5126,11 @@
       <c r="K87" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M87" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>27053</v>
       </c>
@@ -4908,8 +5164,11 @@
       <c r="K88" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M88" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <v>25635</v>
       </c>
@@ -4943,8 +5202,11 @@
       <c r="K89" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M89" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>27054</v>
       </c>
@@ -4978,8 +5240,11 @@
       <c r="K90" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M90" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>26877</v>
       </c>
@@ -5013,8 +5278,11 @@
       <c r="K91" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M91" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <v>25076</v>
       </c>
@@ -5049,7 +5317,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>25021</v>
       </c>
@@ -5084,7 +5352,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>25077</v>
       </c>
@@ -5119,7 +5387,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>25003</v>
       </c>
@@ -5154,7 +5422,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>25005</v>
       </c>
@@ -6156,4 +6424,36 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2D37EF4-75A5-4721-8659-8B0FDD151264}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>90478</v>
+      </c>
+      <c r="B2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Slanger_hylser.xlsx
+++ b/Slanger_hylser.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3D37D3-2455-4B81-94AC-3C14D4E740CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{7B701A88-204F-43FD-9B11-C042844D6F26}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B701A88-204F-43FD-9B11-C042844D6F26}"/>
   </bookViews>
   <sheets>
     <sheet name="Slange+Hylse" sheetId="1" r:id="rId1"/>
@@ -1248,6 +1248,20 @@
   </cellStyles>
   <dxfs count="23">
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1270,20 +1284,6 @@
           <bgColor theme="4"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
     </dxf>
     <dxf>
       <border outline="0">
@@ -1682,7 +1682,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AD8EAC2D-367A-4714-BC50-04B242895EDA}" name="Tabell4" displayName="Tabell4" ref="A1:B2" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AD8EAC2D-367A-4714-BC50-04B242895EDA}" name="Tabell4" displayName="Tabell4" ref="A1:B2" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:B2" xr:uid="{AD8EAC2D-367A-4714-BC50-04B242895EDA}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{ECAA00E3-7280-4EA3-8067-7B2E7B36DD00}" name="Prod.no"/>

--- a/Slanger_hylser.xlsx
+++ b/Slanger_hylser.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\script_2\nuitka\my_slangeprogram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3D37D3-2455-4B81-94AC-3C14D4E740CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F83B29F-B4A5-458F-959A-0533C0FA9FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B701A88-204F-43FD-9B11-C042844D6F26}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="352">
   <si>
     <t>ProV-10 5/8" Bruk Pro2T</t>
   </si>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>25109</v>
       </c>
@@ -2557,11 +2557,8 @@
       <c r="J17" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="M17" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>25527</v>
       </c>
@@ -2592,11 +2589,8 @@
       <c r="J18" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="M18" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>25550</v>
       </c>
@@ -2627,11 +2621,8 @@
       <c r="J19" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="M19" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>25585</v>
       </c>
@@ -2662,11 +2653,8 @@
       <c r="J20" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="M20" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>25517</v>
       </c>
@@ -2697,11 +2685,8 @@
       <c r="J21" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="M21" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>25529</v>
       </c>
@@ -2732,11 +2717,8 @@
       <c r="J22" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="M22" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>25175</v>
       </c>
@@ -2767,11 +2749,8 @@
       <c r="J23" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="M23" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>25530</v>
       </c>
@@ -2802,11 +2781,8 @@
       <c r="J24" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="M24" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>25176</v>
       </c>
@@ -2837,11 +2813,8 @@
       <c r="J25" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="M25" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25501</v>
       </c>
@@ -2871,7 +2844,7 @@
       </c>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25502</v>
       </c>
@@ -2903,7 +2876,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>25503</v>
       </c>
@@ -2935,7 +2908,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>25623</v>
       </c>
@@ -2967,7 +2940,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>25504</v>
       </c>
@@ -2999,7 +2972,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>25505</v>
       </c>
@@ -3031,7 +3004,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>25506</v>
       </c>

--- a/Slanger_hylser.xlsx
+++ b/Slanger_hylser.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\script_2\nuitka\my_slangeprogram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F83B29F-B4A5-458F-959A-0533C0FA9FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F6F0ADA-B2F7-49B9-9824-DAF0D4B2D4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B701A88-204F-43FD-9B11-C042844D6F26}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B701A88-204F-43FD-9B11-C042844D6F26}"/>
   </bookViews>
   <sheets>
     <sheet name="Slange+Hylse" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="354">
   <si>
     <t>ProV-10 5/8" Bruk Pro2T</t>
   </si>
@@ -1096,6 +1096,12 @@
   </si>
   <si>
     <t>ABS Sertifisering/Bevitnelse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M4K-08 MTF 1/2" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">R8-06 3/8" </t>
   </si>
 </sst>
 </file>
@@ -4825,7 +4831,7 @@
         <v>193</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>107</v>
+        <v>352</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>333</v>
@@ -5731,7 +5737,7 @@
         <v>192</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>156</v>
+        <v>353</v>
       </c>
       <c r="J106" s="1"/>
     </row>

--- a/Slanger_hylser.xlsx
+++ b/Slanger_hylser.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\script_2\nuitka\my_slangeprogram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F6F0ADA-B2F7-49B9-9824-DAF0D4B2D4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE303045-C42B-415C-AF50-F78C230B5EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B701A88-204F-43FD-9B11-C042844D6F26}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B701A88-204F-43FD-9B11-C042844D6F26}"/>
   </bookViews>
   <sheets>
     <sheet name="Slange+Hylse" sheetId="1" r:id="rId1"/>
@@ -42,15 +42,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="354">
   <si>
-    <t>ProV-10 5/8" Bruk Pro2T</t>
-  </si>
-  <si>
     <t>ProV-12 3/4" Gates Smooth EN857 2SC WP215bar</t>
   </si>
   <si>
-    <t>ProV-16 1" Bruk Pro2T</t>
-  </si>
-  <si>
     <t>ProV-06 3/8" Gates Smooth EN857 2SC WP330bar</t>
   </si>
   <si>
@@ -1102,6 +1096,12 @@
   </si>
   <si>
     <t xml:space="preserve">R8-06 3/8" </t>
+  </si>
+  <si>
+    <t>ProV-16 1" GATES 2SC Smooth WP165bar</t>
+  </si>
+  <si>
+    <t>ProV-10 5/8" RL50m GATES Smooth EN875 2SC WP250bar,bobbin</t>
   </si>
 </sst>
 </file>
@@ -2031,43 +2031,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="H1" s="7" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="K1" s="7" t="s">
-        <v>334</v>
-      </c>
       <c r="L1" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="M1" s="7" t="s">
         <v>348</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -2075,7 +2075,7 @@
         <v>27056</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C2" s="1">
         <v>420</v>
@@ -2084,19 +2084,19 @@
         <v>26091</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F2" s="2">
         <v>28433</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J2" s="1"/>
     </row>
@@ -2105,7 +2105,7 @@
         <v>27059</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C3" s="1">
         <v>350</v>
@@ -2114,19 +2114,19 @@
         <v>26092</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F3" s="2">
         <v>28434</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J3" s="1"/>
     </row>
@@ -2135,7 +2135,7 @@
         <v>25104</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C4" s="1">
         <v>400</v>
@@ -2144,19 +2144,19 @@
         <v>26090</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F4" s="2">
         <v>28552</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J4" s="1"/>
     </row>
@@ -2165,7 +2165,7 @@
         <v>25064</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C5" s="1">
         <v>450</v>
@@ -2174,22 +2174,22 @@
         <v>26090</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F5" s="2">
         <v>28552</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -2197,7 +2197,7 @@
         <v>25105</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C6" s="1">
         <v>330</v>
@@ -2206,19 +2206,19 @@
         <v>26091</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" s="2">
         <v>28433</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J6" s="1"/>
     </row>
@@ -2227,7 +2227,7 @@
         <v>25073</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C7" s="1">
         <v>390</v>
@@ -2236,22 +2236,22 @@
         <v>26091</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" s="2">
         <v>28433</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -2259,7 +2259,7 @@
         <v>25106</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C8" s="1">
         <v>275</v>
@@ -2268,19 +2268,19 @@
         <v>26092</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F8" s="2">
         <v>28434</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J8" s="1"/>
     </row>
@@ -2289,7 +2289,7 @@
         <v>27060</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C9" s="1">
         <v>350</v>
@@ -2298,22 +2298,22 @@
         <v>26092</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F9" s="2">
         <v>28434</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -2321,7 +2321,7 @@
         <v>25107</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C10" s="1">
         <v>250</v>
@@ -2330,19 +2330,19 @@
         <v>26093</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F10" s="2">
         <v>28686</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J10" s="1"/>
     </row>
@@ -2351,7 +2351,7 @@
         <v>27063</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C11" s="1">
         <v>350</v>
@@ -2360,22 +2360,22 @@
         <v>26093</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F11" s="2">
         <v>28686</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -2383,7 +2383,7 @@
         <v>25108</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C12" s="1">
         <v>215</v>
@@ -2392,19 +2392,19 @@
         <v>26094</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F12" s="2">
         <v>28435</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J12" s="1"/>
     </row>
@@ -2413,7 +2413,7 @@
         <v>27061</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C13" s="1">
         <v>300</v>
@@ -2422,22 +2422,22 @@
         <v>26094</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F13" s="2">
         <v>28435</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -2445,7 +2445,7 @@
         <v>25101</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C14" s="1">
         <v>165</v>
@@ -2454,19 +2454,19 @@
         <v>26095</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F14" s="2">
         <v>28687</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J14" s="1"/>
     </row>
@@ -2475,7 +2475,7 @@
         <v>27065</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C15" s="1">
         <v>230</v>
@@ -2484,22 +2484,22 @@
         <v>26095</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F15" s="2">
         <v>28687</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -2507,7 +2507,7 @@
         <v>25111</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C16" s="1">
         <v>90</v>
@@ -2516,19 +2516,19 @@
         <v>26452</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F16" s="2">
         <v>28690</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J16" s="1"/>
     </row>
@@ -2537,7 +2537,7 @@
         <v>25109</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C17" s="1">
         <v>420</v>
@@ -2546,22 +2546,22 @@
         <v>26749</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F17" s="2">
         <v>38144</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -2569,7 +2569,7 @@
         <v>25527</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C18" s="1">
         <v>385</v>
@@ -2578,22 +2578,22 @@
         <v>26750</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F18" s="2">
         <v>38145</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2601,7 +2601,7 @@
         <v>25550</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C19" s="1">
         <v>385</v>
@@ -2610,22 +2610,22 @@
         <v>26750</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F19" s="2">
         <v>38145</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2633,7 +2633,7 @@
         <v>25585</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C20" s="1">
         <v>350</v>
@@ -2642,22 +2642,22 @@
         <v>26751</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F20" s="2">
         <v>38146</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -2665,7 +2665,7 @@
         <v>25517</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C21" s="1">
         <v>350</v>
@@ -2674,22 +2674,22 @@
         <v>26751</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F21" s="2">
         <v>38146</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2697,7 +2697,7 @@
         <v>25529</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C22" s="1">
         <v>300</v>
@@ -2706,22 +2706,22 @@
         <v>33663</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F22" s="2">
         <v>38147</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2729,7 +2729,7 @@
         <v>25175</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C23" s="1">
         <v>300</v>
@@ -2738,22 +2738,22 @@
         <v>33663</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F23" s="2">
         <v>38147</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2761,7 +2761,7 @@
         <v>25530</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C24" s="1">
         <v>250</v>
@@ -2770,22 +2770,22 @@
         <v>38475</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F24" s="2">
         <v>38148</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2793,7 +2793,7 @@
         <v>25176</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C25" s="1">
         <v>250</v>
@@ -2802,22 +2802,22 @@
         <v>38475</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F25" s="2">
         <v>38148</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2825,7 +2825,7 @@
         <v>25501</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C26" s="1">
         <v>445</v>
@@ -2834,19 +2834,19 @@
         <v>33508</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F26" s="2">
         <v>38141</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J26" s="1"/>
     </row>
@@ -2855,7 +2855,7 @@
         <v>25502</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C27" s="1">
         <v>425</v>
@@ -2864,22 +2864,22 @@
         <v>26747</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F27" s="2">
         <v>38142</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2887,7 +2887,7 @@
         <v>25503</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C28" s="1">
         <v>350</v>
@@ -2896,22 +2896,22 @@
         <v>26748</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F28" s="2">
         <v>38143</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2919,7 +2919,7 @@
         <v>25623</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C29" s="1">
         <v>350</v>
@@ -2928,22 +2928,22 @@
         <v>26749</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F29" s="2">
         <v>38144</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -2951,7 +2951,7 @@
         <v>25504</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C30" s="1">
         <v>320</v>
@@ -2960,22 +2960,22 @@
         <v>26750</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F30" s="2">
         <v>38145</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -2983,7 +2983,7 @@
         <v>25505</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C31" s="5">
         <v>210</v>
@@ -2992,22 +2992,22 @@
         <v>26751</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F31" s="2">
         <v>38146</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -3015,7 +3015,7 @@
         <v>25506</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C32" s="1">
         <v>185</v>
@@ -3024,22 +3024,22 @@
         <v>33663</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F32" s="2">
         <v>38147</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -3047,7 +3047,7 @@
         <v>26851</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C33" s="1">
         <v>130</v>
@@ -3056,28 +3056,28 @@
         <v>26093</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F33" s="2">
         <v>28686</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J33" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K33" t="s">
         <v>333</v>
       </c>
-      <c r="K33" t="s">
-        <v>335</v>
-      </c>
       <c r="M33" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
@@ -3085,7 +3085,7 @@
         <v>26852</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C34" s="1">
         <v>105</v>
@@ -3094,28 +3094,28 @@
         <v>26094</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F34" s="2">
         <v>28435</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J34" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K34" t="s">
         <v>333</v>
       </c>
-      <c r="K34" t="s">
-        <v>335</v>
-      </c>
       <c r="M34" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -3123,7 +3123,7 @@
         <v>26853</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C35" s="1">
         <v>90</v>
@@ -3132,28 +3132,28 @@
         <v>26095</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F35" s="2">
         <v>28687</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J35" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K35" t="s">
         <v>333</v>
       </c>
-      <c r="K35" t="s">
-        <v>335</v>
-      </c>
       <c r="M35" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -3161,7 +3161,7 @@
         <v>26854</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C36" s="1">
         <v>64</v>
@@ -3170,28 +3170,28 @@
         <v>26450</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F36" s="2">
         <v>28688</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J36" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K36" t="s">
         <v>333</v>
       </c>
-      <c r="K36" t="s">
-        <v>335</v>
-      </c>
       <c r="M36" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -3199,7 +3199,7 @@
         <v>26855</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C37" s="1">
         <v>50</v>
@@ -3208,28 +3208,28 @@
         <v>26451</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F37" s="2">
         <v>28689</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="J37" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K37" t="s">
         <v>333</v>
       </c>
-      <c r="K37" t="s">
-        <v>335</v>
-      </c>
       <c r="M37" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -3237,7 +3237,7 @@
         <v>26856</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C38" s="1">
         <v>42</v>
@@ -3246,28 +3246,28 @@
         <v>26452</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F38" s="2">
         <v>28690</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="J38" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K38" t="s">
         <v>333</v>
       </c>
-      <c r="K38" t="s">
-        <v>335</v>
-      </c>
       <c r="M38" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -3275,7 +3275,7 @@
         <v>26857</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C39" s="1">
         <v>125</v>
@@ -3284,28 +3284,28 @@
         <v>26450</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F39" s="2">
         <v>28688</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J39" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K39" t="s">
         <v>333</v>
       </c>
-      <c r="K39" t="s">
-        <v>335</v>
-      </c>
       <c r="M39" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -3313,7 +3313,7 @@
         <v>26858</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C40" s="5">
         <v>90</v>
@@ -3322,28 +3322,28 @@
         <v>26451</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F40" s="2">
         <v>28689</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="J40" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K40" t="s">
         <v>333</v>
       </c>
-      <c r="K40" t="s">
-        <v>335</v>
-      </c>
       <c r="M40" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -3351,7 +3351,7 @@
         <v>26859</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C41" s="1">
         <v>80</v>
@@ -3360,28 +3360,28 @@
         <v>26452</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F41" s="2">
         <v>28690</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="J41" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K41" t="s">
         <v>333</v>
       </c>
-      <c r="K41" t="s">
-        <v>335</v>
-      </c>
       <c r="M41" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
@@ -3389,7 +3389,7 @@
         <v>26774</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C42" s="1">
         <v>210</v>
@@ -3398,25 +3398,25 @@
         <v>37578</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F42" s="2">
         <v>38146</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M42" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
@@ -3424,7 +3424,7 @@
         <v>26844</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C43" s="1">
         <v>210</v>
@@ -3433,25 +3433,25 @@
         <v>37580</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F43" s="2">
         <v>38148</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M43" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
@@ -3459,7 +3459,7 @@
         <v>26784</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C44" s="1">
         <v>280</v>
@@ -3468,25 +3468,25 @@
         <v>37586</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F44" s="2">
         <v>38460</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M44" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -3494,7 +3494,7 @@
         <v>26787</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C45" s="1">
         <v>280</v>
@@ -3503,25 +3503,25 @@
         <v>37578</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F45" s="2">
         <v>38461</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M45" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
@@ -3529,7 +3529,7 @@
         <v>26798</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C46" s="1">
         <v>350</v>
@@ -3538,25 +3538,25 @@
         <v>37584</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F46" s="2">
         <v>38143</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M46" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
@@ -3564,7 +3564,7 @@
         <v>26799</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C47" s="1">
         <v>350</v>
@@ -3573,28 +3573,28 @@
         <v>37585</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F47" s="2">
         <v>27560</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L47">
         <v>5</v>
       </c>
       <c r="M47" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
@@ -3602,7 +3602,7 @@
         <v>26809</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C48" s="1">
         <v>350</v>
@@ -3611,28 +3611,28 @@
         <v>37586</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F48" s="2">
         <v>27561</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L48">
         <v>5</v>
       </c>
       <c r="M48" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -3640,7 +3640,7 @@
         <v>26810</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C49" s="1">
         <v>350</v>
@@ -3649,28 +3649,28 @@
         <v>37581</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F49" s="2">
         <v>27570</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L49">
         <v>5</v>
       </c>
       <c r="M49" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
@@ -3678,7 +3678,7 @@
         <v>26814</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C50" s="1">
         <v>350</v>
@@ -3689,22 +3689,22 @@
         <v>27128</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L50">
         <v>5</v>
       </c>
       <c r="M50" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
@@ -3712,7 +3712,7 @@
         <v>26818</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C51" s="1">
         <v>350</v>
@@ -3723,22 +3723,22 @@
         <v>27127</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L51">
         <v>5</v>
       </c>
       <c r="M51" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
@@ -3746,7 +3746,7 @@
         <v>26827</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C52" s="1">
         <v>420</v>
@@ -3755,28 +3755,28 @@
         <v>37585</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F52" s="2">
         <v>27560</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L52">
         <v>5</v>
       </c>
       <c r="M52" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
@@ -3784,7 +3784,7 @@
         <v>26831</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C53" s="1">
         <v>420</v>
@@ -3793,28 +3793,28 @@
         <v>37586</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F53" s="2">
         <v>27561</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L53">
         <v>5</v>
       </c>
       <c r="M53" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
@@ -3822,7 +3822,7 @@
         <v>26835</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C54" s="1">
         <v>420</v>
@@ -3831,28 +3831,28 @@
         <v>37581</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F54" s="2">
         <v>27570</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L54">
         <v>5</v>
       </c>
       <c r="M54" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -3860,7 +3860,7 @@
         <v>26838</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C55" s="1">
         <v>420</v>
@@ -3869,28 +3869,28 @@
         <v>37579</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F55" s="2">
         <v>27128</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L55">
         <v>5</v>
       </c>
       <c r="M55" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
@@ -3898,7 +3898,7 @@
         <v>26841</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C56" s="1">
         <v>420</v>
@@ -3907,28 +3907,28 @@
         <v>37580</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F56" s="2">
         <v>27127</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L56">
         <v>5</v>
       </c>
       <c r="M56" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
@@ -3936,7 +3936,7 @@
         <v>26548</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C57" s="1">
         <v>420</v>
@@ -3945,28 +3945,28 @@
         <v>26090</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F57" s="2">
         <v>28552</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J57" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K57" t="s">
         <v>333</v>
       </c>
-      <c r="K57" t="s">
-        <v>335</v>
-      </c>
       <c r="M57" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
@@ -3974,7 +3974,7 @@
         <v>27008</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C58" s="1">
         <v>350</v>
@@ -3983,28 +3983,28 @@
         <v>26091</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F58" s="2">
         <v>28433</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="J58" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K58" t="s">
         <v>333</v>
       </c>
-      <c r="K58" t="s">
-        <v>335</v>
-      </c>
       <c r="M58" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
@@ -4012,7 +4012,7 @@
         <v>27009</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C59" s="1">
         <v>296</v>
@@ -4021,28 +4021,28 @@
         <v>26092</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F59" s="2">
         <v>28434</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="J59" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K59" t="s">
         <v>333</v>
       </c>
-      <c r="K59" t="s">
-        <v>335</v>
-      </c>
       <c r="M59" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
@@ -4050,7 +4050,7 @@
         <v>25619</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C60" s="5">
         <v>262</v>
@@ -4059,28 +4059,28 @@
         <v>26093</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F60" s="2">
         <v>28686</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="J60" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K60" t="s">
         <v>333</v>
       </c>
-      <c r="K60" t="s">
-        <v>335</v>
-      </c>
       <c r="M60" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -4088,7 +4088,7 @@
         <v>27043</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C61" s="1">
         <v>241</v>
@@ -4097,28 +4097,28 @@
         <v>26094</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F61" s="2">
         <v>28435</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="J61" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K61" t="s">
         <v>333</v>
       </c>
-      <c r="K61" t="s">
-        <v>335</v>
-      </c>
       <c r="M61" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -4126,7 +4126,7 @@
         <v>26549</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C62" s="1">
         <v>172</v>
@@ -4135,28 +4135,28 @@
         <v>26095</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F62" s="2">
         <v>28687</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="J62" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K62" t="s">
         <v>333</v>
       </c>
-      <c r="K62" t="s">
-        <v>335</v>
-      </c>
       <c r="M62" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -4164,7 +4164,7 @@
         <v>26860</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C63" s="1">
         <v>210</v>
@@ -4173,28 +4173,28 @@
         <v>26009</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F63" s="2">
         <v>28590</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="J63" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K63" t="s">
         <v>333</v>
       </c>
-      <c r="K63" t="s">
-        <v>335</v>
-      </c>
       <c r="M63" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
@@ -4202,7 +4202,7 @@
         <v>26861</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C64" s="1">
         <v>210</v>
@@ -4211,28 +4211,28 @@
         <v>26009</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F64" s="2">
         <v>28590</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J64" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K64" t="s">
         <v>333</v>
       </c>
-      <c r="K64" t="s">
-        <v>335</v>
-      </c>
       <c r="M64" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
@@ -4240,7 +4240,7 @@
         <v>26864</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C65" s="1">
         <v>210</v>
@@ -4249,28 +4249,28 @@
         <v>26010</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F65" s="2">
         <v>28591</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J65" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K65" t="s">
         <v>333</v>
       </c>
-      <c r="K65" t="s">
-        <v>335</v>
-      </c>
       <c r="M65" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
@@ -4278,7 +4278,7 @@
         <v>26865</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C66" s="5">
         <v>210</v>
@@ -4287,28 +4287,28 @@
         <v>26010</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F66" s="2">
         <v>28591</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="J66" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K66" t="s">
         <v>333</v>
       </c>
-      <c r="K66" t="s">
-        <v>335</v>
-      </c>
       <c r="M66" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
@@ -4316,7 +4316,7 @@
         <v>26866</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C67" s="5">
         <v>210</v>
@@ -4325,28 +4325,28 @@
         <v>26011</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F67" s="2">
         <v>28592</v>
       </c>
       <c r="G67" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K67" t="s">
+        <v>333</v>
+      </c>
+      <c r="M67" t="s">
         <v>347</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="K67" t="s">
-        <v>335</v>
-      </c>
-      <c r="M67" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
@@ -4354,7 +4354,7 @@
         <v>26867</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C68" s="5">
         <v>210</v>
@@ -4363,28 +4363,28 @@
         <v>26011</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F68" s="2">
         <v>28592</v>
       </c>
       <c r="G68" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K68" t="s">
+        <v>333</v>
+      </c>
+      <c r="M68" t="s">
         <v>347</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="I68" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="K68" t="s">
-        <v>335</v>
-      </c>
-      <c r="M68" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
@@ -4392,7 +4392,7 @@
         <v>26868</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C69" s="1">
         <v>210</v>
@@ -4401,28 +4401,28 @@
         <v>26093</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F69" s="2">
         <v>28686</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="J69" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K69" t="s">
         <v>333</v>
       </c>
-      <c r="K69" t="s">
-        <v>335</v>
-      </c>
       <c r="M69" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
@@ -4430,7 +4430,7 @@
         <v>58850</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C70" s="1">
         <v>210</v>
@@ -4439,28 +4439,28 @@
         <v>26093</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F70" s="2">
         <v>28686</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J70" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K70" t="s">
         <v>333</v>
       </c>
-      <c r="K70" t="s">
-        <v>335</v>
-      </c>
       <c r="M70" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
@@ -4468,7 +4468,7 @@
         <v>26870</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C71" s="1">
         <v>210</v>
@@ -4477,28 +4477,28 @@
         <v>26094</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F71" s="2">
         <v>28435</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J71" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K71" t="s">
         <v>333</v>
       </c>
-      <c r="K71" t="s">
-        <v>335</v>
-      </c>
       <c r="M71" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
@@ -4506,7 +4506,7 @@
         <v>26869</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C72" s="1">
         <v>210</v>
@@ -4515,28 +4515,28 @@
         <v>26094</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F72" s="2">
         <v>28435</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J72" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K72" t="s">
         <v>333</v>
       </c>
-      <c r="K72" t="s">
-        <v>335</v>
-      </c>
       <c r="M72" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
@@ -4544,7 +4544,7 @@
         <v>25637</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C73" s="5">
         <v>210</v>
@@ -4553,28 +4553,28 @@
         <v>26095</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F73" s="2">
         <v>28687</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="J73" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K73" t="s">
         <v>333</v>
       </c>
-      <c r="K73" t="s">
-        <v>335</v>
-      </c>
       <c r="M73" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
@@ -4582,7 +4582,7 @@
         <v>26871</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C74" s="1">
         <v>210</v>
@@ -4591,28 +4591,28 @@
         <v>26095</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F74" s="2">
         <v>28687</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J74" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K74" t="s">
         <v>333</v>
       </c>
-      <c r="K74" t="s">
-        <v>335</v>
-      </c>
       <c r="M74" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
@@ -4620,7 +4620,7 @@
         <v>25621</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C75" s="1">
         <v>280</v>
@@ -4629,28 +4629,28 @@
         <v>26090</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F75" s="2">
         <v>28552</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J75" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K75" t="s">
         <v>333</v>
       </c>
-      <c r="K75" t="s">
-        <v>335</v>
-      </c>
       <c r="M75" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
@@ -4658,7 +4658,7 @@
         <v>25065</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C76" s="1">
         <v>280</v>
@@ -4667,28 +4667,28 @@
         <v>26090</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F76" s="2">
         <v>28552</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J76" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K76" t="s">
         <v>333</v>
       </c>
-      <c r="K76" t="s">
-        <v>335</v>
-      </c>
       <c r="M76" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
@@ -4696,7 +4696,7 @@
         <v>25624</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C77" s="1">
         <v>280</v>
@@ -4705,28 +4705,28 @@
         <v>26091</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F77" s="2">
         <v>28433</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J77" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K77" t="s">
         <v>333</v>
       </c>
-      <c r="K77" t="s">
-        <v>335</v>
-      </c>
       <c r="M77" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
@@ -4734,7 +4734,7 @@
         <v>25066</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C78" s="1">
         <v>280</v>
@@ -4743,28 +4743,28 @@
         <v>26091</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F78" s="2">
         <v>28433</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="J78" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K78" t="s">
         <v>333</v>
       </c>
-      <c r="K78" t="s">
-        <v>335</v>
-      </c>
       <c r="M78" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
@@ -4772,7 +4772,7 @@
         <v>25651</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C79" s="1">
         <v>280</v>
@@ -4781,28 +4781,28 @@
         <v>26091</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F79" s="2">
         <v>28433</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J79" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K79" t="s">
         <v>333</v>
       </c>
-      <c r="K79" t="s">
-        <v>335</v>
-      </c>
       <c r="M79" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
@@ -4810,7 +4810,7 @@
         <v>25068</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C80" s="1">
         <v>280</v>
@@ -4819,28 +4819,28 @@
         <v>26092</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F80" s="2">
         <v>28434</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J80" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K80" t="s">
         <v>333</v>
       </c>
-      <c r="K80" t="s">
-        <v>335</v>
-      </c>
       <c r="M80" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
@@ -4848,7 +4848,7 @@
         <v>26872</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C81" s="1">
         <v>280</v>
@@ -4857,28 +4857,28 @@
         <v>26093</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F81" s="2">
         <v>28686</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="J81" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K81" t="s">
         <v>333</v>
       </c>
-      <c r="K81" t="s">
-        <v>335</v>
-      </c>
       <c r="M81" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
@@ -4886,7 +4886,7 @@
         <v>26873</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C82" s="1">
         <v>280</v>
@@ -4895,28 +4895,28 @@
         <v>26093</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F82" s="2">
         <v>28686</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J82" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K82" t="s">
         <v>333</v>
       </c>
-      <c r="K82" t="s">
-        <v>335</v>
-      </c>
       <c r="M82" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
@@ -4924,7 +4924,7 @@
         <v>25636</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C83" s="5">
         <v>280</v>
@@ -4933,28 +4933,28 @@
         <v>26094</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F83" s="2">
         <v>28435</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J83" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K83" t="s">
         <v>333</v>
       </c>
-      <c r="K83" t="s">
-        <v>335</v>
-      </c>
       <c r="M83" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
@@ -4962,7 +4962,7 @@
         <v>26874</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C84" s="1">
         <v>280</v>
@@ -4971,28 +4971,28 @@
         <v>26094</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F84" s="2">
         <v>28435</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="J84" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K84" t="s">
         <v>333</v>
       </c>
-      <c r="K84" t="s">
-        <v>335</v>
-      </c>
       <c r="M84" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
@@ -5000,7 +5000,7 @@
         <v>25102</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C85" s="1">
         <v>350</v>
@@ -5009,28 +5009,28 @@
         <v>26090</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F85" s="2">
         <v>28552</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J85" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K85" t="s">
         <v>333</v>
       </c>
-      <c r="K85" t="s">
-        <v>335</v>
-      </c>
       <c r="M85" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
@@ -5038,7 +5038,7 @@
         <v>27052</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C86" s="1">
         <v>350</v>
@@ -5047,28 +5047,28 @@
         <v>26090</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F86" s="2">
         <v>28552</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="J86" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K86" t="s">
         <v>333</v>
       </c>
-      <c r="K86" t="s">
-        <v>335</v>
-      </c>
       <c r="M86" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
@@ -5076,7 +5076,7 @@
         <v>26876</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C87" s="1">
         <v>350</v>
@@ -5085,28 +5085,28 @@
         <v>26091</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F87" s="2">
         <v>28433</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="J87" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K87" t="s">
         <v>333</v>
       </c>
-      <c r="K87" t="s">
-        <v>335</v>
-      </c>
       <c r="M87" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
@@ -5114,7 +5114,7 @@
         <v>27053</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C88" s="1">
         <v>350</v>
@@ -5123,28 +5123,28 @@
         <v>26091</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F88" s="2">
         <v>28433</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H88" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J88" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K88" t="s">
         <v>333</v>
       </c>
-      <c r="K88" t="s">
-        <v>335</v>
-      </c>
       <c r="M88" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
@@ -5152,7 +5152,7 @@
         <v>25635</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C89" s="5">
         <v>350</v>
@@ -5161,28 +5161,28 @@
         <v>26091</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F89" s="6">
         <v>28433</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I89" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="J89" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K89" t="s">
         <v>333</v>
       </c>
-      <c r="K89" t="s">
-        <v>335</v>
-      </c>
       <c r="M89" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
@@ -5190,7 +5190,7 @@
         <v>27054</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C90" s="1">
         <v>350</v>
@@ -5199,28 +5199,28 @@
         <v>26091</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F90" s="2">
         <v>28433</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J90" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K90" t="s">
         <v>333</v>
       </c>
-      <c r="K90" t="s">
-        <v>335</v>
-      </c>
       <c r="M90" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
@@ -5228,7 +5228,7 @@
         <v>26877</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C91" s="1">
         <v>420</v>
@@ -5237,28 +5237,28 @@
         <v>26090</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F91" s="2">
         <v>28552</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="J91" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K91" t="s">
         <v>333</v>
       </c>
-      <c r="K91" t="s">
-        <v>335</v>
-      </c>
       <c r="M91" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
@@ -5266,7 +5266,7 @@
         <v>25076</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C92" s="5">
         <v>400</v>
@@ -5275,25 +5275,25 @@
         <v>26090</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F92" s="6">
         <v>28552</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J92" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K92" t="s">
         <v>333</v>
-      </c>
-      <c r="K92" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
@@ -5301,7 +5301,7 @@
         <v>25021</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C93" s="1">
         <v>330</v>
@@ -5310,25 +5310,25 @@
         <v>26091</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F93" s="2">
         <v>28433</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J93" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K93" t="s">
         <v>333</v>
-      </c>
-      <c r="K93" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
@@ -5336,7 +5336,7 @@
         <v>25077</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C94" s="1">
         <v>275</v>
@@ -5345,33 +5345,33 @@
         <v>26092</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F94" s="2">
         <v>28434</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J94" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K94" t="s">
         <v>333</v>
-      </c>
-      <c r="K94" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>25003</v>
+        <v>25004</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>0</v>
+        <v>353</v>
       </c>
       <c r="C95" s="1">
         <v>215</v>
@@ -5380,25 +5380,25 @@
         <v>26093</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F95" s="2">
         <v>28686</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="J95" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K95" t="s">
         <v>333</v>
-      </c>
-      <c r="K95" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
@@ -5406,7 +5406,7 @@
         <v>25005</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C96" s="1">
         <v>165</v>
@@ -5415,25 +5415,25 @@
         <v>26094</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F96" s="2">
         <v>28435</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J96" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K96" t="s">
         <v>333</v>
-      </c>
-      <c r="K96" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -5441,7 +5441,7 @@
         <v>25006</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>2</v>
+        <v>352</v>
       </c>
       <c r="C97" s="1">
         <v>165</v>
@@ -5450,25 +5450,25 @@
         <v>26095</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F97" s="2">
         <v>28687</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J97" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K97" t="s">
         <v>333</v>
-      </c>
-      <c r="K97" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -5476,7 +5476,7 @@
         <v>25032</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C98" s="5">
         <v>190</v>
@@ -5485,19 +5485,19 @@
         <v>26018</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F98" s="6">
         <v>28553</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J98" s="1"/>
     </row>
@@ -5506,7 +5506,7 @@
         <v>25039</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C99" s="1">
         <v>155</v>
@@ -5515,19 +5515,19 @@
         <v>26019</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F99" s="2">
         <v>28554</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J99" s="1"/>
     </row>
@@ -5536,7 +5536,7 @@
         <v>25034</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C100" s="1">
         <v>155</v>
@@ -5545,19 +5545,19 @@
         <v>26019</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F100" s="2">
         <v>28554</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J100" s="1"/>
     </row>
@@ -5566,7 +5566,7 @@
         <v>25036</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C101" s="1">
         <v>140</v>
@@ -5575,19 +5575,19 @@
         <v>26020</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F101" s="2">
         <v>28345</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J101" s="1"/>
     </row>
@@ -5596,7 +5596,7 @@
         <v>25037</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C102" s="1">
         <v>105</v>
@@ -5605,19 +5605,19 @@
         <v>26021</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F102" s="2">
         <v>28555</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J102" s="1"/>
     </row>
@@ -5626,7 +5626,7 @@
         <v>25038</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C103" s="1">
         <v>87</v>
@@ -5635,19 +5635,19 @@
         <v>26022</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F103" s="2">
         <v>28556</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="J103" s="1"/>
     </row>
@@ -5656,7 +5656,7 @@
         <v>25040</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C104" s="1">
         <v>350</v>
@@ -5665,19 +5665,19 @@
         <v>26018</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F104" s="2">
         <v>28553</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H104" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J104" s="1"/>
     </row>
@@ -5686,7 +5686,7 @@
         <v>25016</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C105" s="1">
         <v>350</v>
@@ -5695,19 +5695,19 @@
         <v>26018</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F105" s="2">
         <v>28553</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J105" s="1"/>
     </row>
@@ -5716,7 +5716,7 @@
         <v>25042</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C106" s="1">
         <v>280</v>
@@ -5725,19 +5725,19 @@
         <v>26019</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F106" s="2">
         <v>28554</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H106" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J106" s="1"/>
     </row>
@@ -5746,7 +5746,7 @@
         <v>25606</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C107" s="5">
         <v>280</v>
@@ -5755,19 +5755,19 @@
         <v>26019</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F107" s="6">
         <v>28554</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="J107" s="1"/>
     </row>
@@ -5776,7 +5776,7 @@
         <v>25044</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C108" s="1">
         <v>245</v>
@@ -5785,19 +5785,19 @@
         <v>26020</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F108" s="2">
         <v>28345</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H108" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="J108" s="1"/>
     </row>
@@ -5806,7 +5806,7 @@
         <v>25607</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C109" s="1">
         <v>245</v>
@@ -5815,19 +5815,19 @@
         <v>26020</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F109" s="2">
         <v>28345</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J109" s="1"/>
     </row>
@@ -5836,7 +5836,7 @@
         <v>25045</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C110" s="1">
         <v>165</v>
@@ -5845,19 +5845,19 @@
         <v>26022</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F110" s="2">
         <v>28556</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H110" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J110" s="1"/>
     </row>
@@ -5866,7 +5866,7 @@
         <v>25642</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C111" s="5">
         <v>162</v>
@@ -5875,19 +5875,19 @@
         <v>26022</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F111" s="6">
         <v>28556</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="J111" s="1"/>
     </row>
@@ -5896,7 +5896,7 @@
         <v>25616</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C112" s="1">
         <v>140</v>
@@ -5905,19 +5905,19 @@
         <v>26023</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F112" s="2">
         <v>28557</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H112" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="J112" s="1"/>
     </row>
@@ -5926,7 +5926,7 @@
         <v>25120</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C113" s="1">
         <v>142</v>
@@ -5935,19 +5935,19 @@
         <v>26023</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F113" s="2">
         <v>28557</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="J113" s="1"/>
     </row>
@@ -5956,7 +5956,7 @@
         <v>25047</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C114" s="1">
         <v>233</v>
@@ -5965,19 +5965,19 @@
         <v>26024</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F114" s="2">
         <v>28691</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H114" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="J114" s="1"/>
     </row>
@@ -5986,7 +5986,7 @@
         <v>25048</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C115" s="1">
         <v>188</v>
@@ -5995,19 +5995,19 @@
         <v>26025</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F115" s="2">
         <v>28692</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="J115" s="1"/>
     </row>
@@ -6016,7 +6016,7 @@
         <v>25049</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C116" s="1">
         <v>160</v>
@@ -6025,19 +6025,19 @@
         <v>26001</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F116" s="2">
         <v>28693</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H116" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J116" s="1"/>
     </row>
@@ -6046,7 +6046,7 @@
         <v>25050</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C117" s="5">
         <v>120</v>
@@ -6055,19 +6055,19 @@
         <v>26455</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F117" s="6">
         <v>28694</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I117" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="J117" s="1"/>
     </row>
@@ -6076,7 +6076,7 @@
         <v>27055</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C118" s="1">
         <v>400</v>
@@ -6085,19 +6085,19 @@
         <v>26091</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F118" s="2">
         <v>28433</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H118" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J118" s="1"/>
     </row>
@@ -6106,7 +6106,7 @@
         <v>25012</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C119" s="5">
         <v>80</v>
@@ -6115,22 +6115,22 @@
         <v>26452</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F119" s="2">
         <v>28690</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I119" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -6138,7 +6138,7 @@
         <v>25010</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C120" s="5">
         <v>125</v>
@@ -6147,22 +6147,22 @@
         <v>26450</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F120" s="2">
         <v>28688</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H120" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I120" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -6170,7 +6170,7 @@
         <v>25011</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C121" s="5">
         <v>90</v>
@@ -6179,22 +6179,22 @@
         <v>26451</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F121" s="2">
         <v>28689</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I121" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -6215,10 +6215,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -6226,7 +6226,7 @@
         <v>90011</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -6234,7 +6234,7 @@
         <v>90012</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6242,7 +6242,7 @@
         <v>90013</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -6250,7 +6250,7 @@
         <v>90800</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -6271,10 +6271,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -6282,7 +6282,7 @@
         <v>90094</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -6290,7 +6290,7 @@
         <v>90095</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6298,7 +6298,7 @@
         <v>90096</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -6306,7 +6306,7 @@
         <v>90097</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -6314,7 +6314,7 @@
         <v>90098</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -6322,7 +6322,7 @@
         <v>90099</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -6330,7 +6330,7 @@
         <v>900101</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -6338,7 +6338,7 @@
         <v>900102</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -6346,7 +6346,7 @@
         <v>900103</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -6367,10 +6367,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -6378,7 +6378,7 @@
         <v>90015</v>
       </c>
       <c r="B2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -6386,7 +6386,7 @@
         <v>90016</v>
       </c>
       <c r="B3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6394,7 +6394,7 @@
         <v>90017</v>
       </c>
       <c r="B4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -6415,10 +6415,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -6426,7 +6426,7 @@
         <v>90478</v>
       </c>
       <c r="B2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>

--- a/Slanger_hylser.xlsx
+++ b/Slanger_hylser.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\script_2\nuitka\my_slangeprogram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE303045-C42B-415C-AF50-F78C230B5EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{01D83835-0CAA-4E04-9BFF-1C92733A8ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B701A88-204F-43FD-9B11-C042844D6F26}"/>
   </bookViews>
@@ -5409,7 +5409,7 @@
         <v>0</v>
       </c>
       <c r="C96" s="1">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="D96" s="2">
         <v>26094</v>

--- a/Slanger_hylser.xlsx
+++ b/Slanger_hylser.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\script_2\nuitka\my_slangeprogram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01D83835-0CAA-4E04-9BFF-1C92733A8ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B2DD59-5D50-4804-B067-88B04BCADBF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B701A88-204F-43FD-9B11-C042844D6F26}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{7B701A88-204F-43FD-9B11-C042844D6F26}"/>
   </bookViews>
   <sheets>
     <sheet name="Slange+Hylse" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="355">
   <si>
     <t>ProV-12 3/4" Gates Smooth EN857 2SC WP215bar</t>
   </si>
@@ -1102,6 +1102,9 @@
   </si>
   <si>
     <t>ProV-10 5/8" RL50m GATES Smooth EN875 2SC WP250bar,bobbin</t>
+  </si>
+  <si>
+    <t>Rengjøring Ultraclean 1 propp etter påpressing, plugges</t>
   </si>
 </sst>
 </file>
@@ -1255,16 +1258,16 @@
   <dxfs count="23">
     <dxf>
       <border outline="0">
-        <top style="thin">
+        <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
-        </top>
+        </bottom>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <top style="thin">
           <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
@@ -1688,8 +1691,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AD8EAC2D-367A-4714-BC50-04B242895EDA}" name="Tabell4" displayName="Tabell4" ref="A1:B2" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:B2" xr:uid="{AD8EAC2D-367A-4714-BC50-04B242895EDA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AD8EAC2D-367A-4714-BC50-04B242895EDA}" name="Tabell4" displayName="Tabell4" ref="A1:B3" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
+  <autoFilter ref="A1:B3" xr:uid="{AD8EAC2D-367A-4714-BC50-04B242895EDA}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{ECAA00E3-7280-4EA3-8067-7B2E7B36DD00}" name="Prod.no"/>
     <tableColumn id="2" xr3:uid="{4E35FD51-CBD8-4747-8C56-419ECA215C8E}" name="Beskrivelse"/>
@@ -6407,10 +6410,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2D37EF4-75A5-4721-8659-8B0FDD151264}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -6429,10 +6432,19 @@
         <v>349</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>90003</v>
+      </c>
+      <c r="B3" t="s">
+        <v>354</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Slanger_hylser.xlsx
+++ b/Slanger_hylser.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\script_2\nuitka\my_slangeprogram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B2DD59-5D50-4804-B067-88B04BCADBF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5071095F-D874-4295-9DEB-C725A4536EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{7B701A88-204F-43FD-9B11-C042844D6F26}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B701A88-204F-43FD-9B11-C042844D6F26}"/>
   </bookViews>
   <sheets>
     <sheet name="Slange+Hylse" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="356">
   <si>
     <t>ProV-12 3/4" Gates Smooth EN857 2SC WP215bar</t>
   </si>
@@ -1105,6 +1105,9 @@
   </si>
   <si>
     <t>Rengjøring Ultraclean 1 propp etter påpressing, plugges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M3K-08 MTF 1/2" </t>
   </si>
 </sst>
 </file>
@@ -1256,44 +1259,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="23">
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <border outline="0">
         <top style="thin">
@@ -1616,6 +1581,44 @@
         </horizontal>
       </border>
     </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1630,22 +1633,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{13F7CE61-B835-454D-AFC3-CEB551034587}" name="Tabell2" displayName="Tabell2" ref="A1:M121" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{13F7CE61-B835-454D-AFC3-CEB551034587}" name="Tabell2" displayName="Tabell2" ref="A1:M121" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18">
   <autoFilter ref="A1:M121" xr:uid="{13F7CE61-B835-454D-AFC3-CEB551034587}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H117">
     <sortCondition ref="B1:B117"/>
   </sortState>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{251763FC-B91D-4A89-B8B7-24A309DCF786}" name="Prod.no" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{6F1BDC04-FAD1-44CE-988A-F11C7CD266F7}" name="Beskrivelse" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{6C6D1FB6-7476-4DFA-9F05-D4D8C95C03BB}" name="Trykk(bar)" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{320FBDDA-F2D6-4BC8-8BC6-EFEA77CEB457}" name="Stål hylse(Posd.no)" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{132BF19B-0DFE-4C8D-85C6-693B0B60662C}" name="Stål hylse(beskrivelse)" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{C92843E4-878E-4C75-8377-AFF9EEC911E7}" name="316 hylse(Posd.no)" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{08D3EFC1-C39C-4CE2-A7AC-FB42CCC5D810}" name="316 hylse(beskrivelse)" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{E6D17188-97DD-4D95-A901-3FD70A9FCA0A}" name="Dimensjon" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{56F2FEA3-E0B4-4E55-964E-D824A8370847}" name="Beskrivelse_2" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{3F602BE4-7A8F-4F61-BED5-79A8D52CC744}" name="Type Approval" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{251763FC-B91D-4A89-B8B7-24A309DCF786}" name="Prod.no" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{6F1BDC04-FAD1-44CE-988A-F11C7CD266F7}" name="Beskrivelse" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{6C6D1FB6-7476-4DFA-9F05-D4D8C95C03BB}" name="Trykk(bar)" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{320FBDDA-F2D6-4BC8-8BC6-EFEA77CEB457}" name="Stål hylse(Posd.no)" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{132BF19B-0DFE-4C8D-85C6-693B0B60662C}" name="Stål hylse(beskrivelse)" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{C92843E4-878E-4C75-8377-AFF9EEC911E7}" name="316 hylse(Posd.no)" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{08D3EFC1-C39C-4CE2-A7AC-FB42CCC5D810}" name="316 hylse(beskrivelse)" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{E6D17188-97DD-4D95-A901-3FD70A9FCA0A}" name="Dimensjon" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{56F2FEA3-E0B4-4E55-964E-D824A8370847}" name="Beskrivelse_2" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{3F602BE4-7A8F-4F61-BED5-79A8D52CC744}" name="Type Approval" dataDxfId="8"/>
     <tableColumn id="11" xr3:uid="{87DF9766-F9A2-4EE1-82F9-950B951AB038}" name="produsent"/>
     <tableColumn id="12" xr3:uid="{C2EE9A93-1E62-4D6D-B9A5-962480D9AE7C}" name="Kolonne1"/>
     <tableColumn id="13" xr3:uid="{4D008D02-01AE-4A0B-A561-8C5593D5372F}" name="Type Approval1"/>
@@ -1655,7 +1658,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6BEF41EF-32DD-420C-B223-1654EADDF20B}" name="Tabell3" displayName="Tabell3" ref="A1:B5" totalsRowShown="0" headerRowDxfId="10" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6BEF41EF-32DD-420C-B223-1654EADDF20B}" name="Tabell3" displayName="Tabell3" ref="A1:B5" totalsRowShown="0" headerRowDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="A1:B5" xr:uid="{6BEF41EF-32DD-420C-B223-1654EADDF20B}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{124E6E90-798A-432B-86E3-10556B79F89A}" name="Prod.no"/>
@@ -1666,7 +1669,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7DBC489E-59EF-4879-9FE4-76393ACAC418}" name="Tabell6" displayName="Tabell6" ref="A1:B10" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7DBC489E-59EF-4879-9FE4-76393ACAC418}" name="Tabell6" displayName="Tabell6" ref="A1:B10" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
   <autoFilter ref="A1:B10" xr:uid="{7DBC489E-59EF-4879-9FE4-76393ACAC418}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B10">
     <sortCondition ref="A1:A10"/>
@@ -1680,7 +1683,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3CAE563-162D-4C3A-BEDE-177DC1706CEB}" name="Tabell1" displayName="Tabell1" ref="A1:B4" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3CAE563-162D-4C3A-BEDE-177DC1706CEB}" name="Tabell1" displayName="Tabell1" ref="A1:B4" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:B4" xr:uid="{A3CAE563-162D-4C3A-BEDE-177DC1706CEB}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{35D6F108-6881-4EB0-9336-2AB6B9CC07A8}" name="Prod.no"/>
@@ -1691,7 +1694,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AD8EAC2D-367A-4714-BC50-04B242895EDA}" name="Tabell4" displayName="Tabell4" ref="A1:B3" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AD8EAC2D-367A-4714-BC50-04B242895EDA}" name="Tabell4" displayName="Tabell4" ref="A1:B3" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20">
   <autoFilter ref="A1:B3" xr:uid="{AD8EAC2D-367A-4714-BC50-04B242895EDA}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{ECAA00E3-7280-4EA3-8067-7B2E7B36DD00}" name="Prod.no"/>
@@ -4378,7 +4381,7 @@
         <v>191</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>93</v>
+        <v>355</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>331</v>

--- a/Slanger_hylser.xlsx
+++ b/Slanger_hylser.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5071095F-D874-4295-9DEB-C725A4536EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B701A88-204F-43FD-9B11-C042844D6F26}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B701A88-204F-43FD-9B11-C042844D6F26}"/>
   </bookViews>
   <sheets>
     <sheet name="Slange+Hylse" sheetId="1" r:id="rId1"/>
@@ -1259,6 +1259,44 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="23">
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <border outline="0">
         <top style="thin">
@@ -1581,44 +1619,6 @@
         </horizontal>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1633,22 +1633,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{13F7CE61-B835-454D-AFC3-CEB551034587}" name="Tabell2" displayName="Tabell2" ref="A1:M121" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{13F7CE61-B835-454D-AFC3-CEB551034587}" name="Tabell2" displayName="Tabell2" ref="A1:M121" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21">
   <autoFilter ref="A1:M121" xr:uid="{13F7CE61-B835-454D-AFC3-CEB551034587}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H117">
     <sortCondition ref="B1:B117"/>
   </sortState>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{251763FC-B91D-4A89-B8B7-24A309DCF786}" name="Prod.no" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{6F1BDC04-FAD1-44CE-988A-F11C7CD266F7}" name="Beskrivelse" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{6C6D1FB6-7476-4DFA-9F05-D4D8C95C03BB}" name="Trykk(bar)" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{320FBDDA-F2D6-4BC8-8BC6-EFEA77CEB457}" name="Stål hylse(Posd.no)" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{132BF19B-0DFE-4C8D-85C6-693B0B60662C}" name="Stål hylse(beskrivelse)" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{C92843E4-878E-4C75-8377-AFF9EEC911E7}" name="316 hylse(Posd.no)" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{08D3EFC1-C39C-4CE2-A7AC-FB42CCC5D810}" name="316 hylse(beskrivelse)" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{E6D17188-97DD-4D95-A901-3FD70A9FCA0A}" name="Dimensjon" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{56F2FEA3-E0B4-4E55-964E-D824A8370847}" name="Beskrivelse_2" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{3F602BE4-7A8F-4F61-BED5-79A8D52CC744}" name="Type Approval" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{251763FC-B91D-4A89-B8B7-24A309DCF786}" name="Prod.no" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{6F1BDC04-FAD1-44CE-988A-F11C7CD266F7}" name="Beskrivelse" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{6C6D1FB6-7476-4DFA-9F05-D4D8C95C03BB}" name="Trykk(bar)" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{320FBDDA-F2D6-4BC8-8BC6-EFEA77CEB457}" name="Stål hylse(Posd.no)" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{132BF19B-0DFE-4C8D-85C6-693B0B60662C}" name="Stål hylse(beskrivelse)" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{C92843E4-878E-4C75-8377-AFF9EEC911E7}" name="316 hylse(Posd.no)" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{08D3EFC1-C39C-4CE2-A7AC-FB42CCC5D810}" name="316 hylse(beskrivelse)" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{E6D17188-97DD-4D95-A901-3FD70A9FCA0A}" name="Dimensjon" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{56F2FEA3-E0B4-4E55-964E-D824A8370847}" name="Beskrivelse_2" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{3F602BE4-7A8F-4F61-BED5-79A8D52CC744}" name="Type Approval" dataDxfId="11"/>
     <tableColumn id="11" xr3:uid="{87DF9766-F9A2-4EE1-82F9-950B951AB038}" name="produsent"/>
     <tableColumn id="12" xr3:uid="{C2EE9A93-1E62-4D6D-B9A5-962480D9AE7C}" name="Kolonne1"/>
     <tableColumn id="13" xr3:uid="{4D008D02-01AE-4A0B-A561-8C5593D5372F}" name="Type Approval1"/>
@@ -1658,7 +1658,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6BEF41EF-32DD-420C-B223-1654EADDF20B}" name="Tabell3" displayName="Tabell3" ref="A1:B5" totalsRowShown="0" headerRowDxfId="7" tableBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6BEF41EF-32DD-420C-B223-1654EADDF20B}" name="Tabell3" displayName="Tabell3" ref="A1:B5" totalsRowShown="0" headerRowDxfId="10" tableBorderDxfId="9">
   <autoFilter ref="A1:B5" xr:uid="{6BEF41EF-32DD-420C-B223-1654EADDF20B}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{124E6E90-798A-432B-86E3-10556B79F89A}" name="Prod.no"/>
@@ -1669,7 +1669,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7DBC489E-59EF-4879-9FE4-76393ACAC418}" name="Tabell6" displayName="Tabell6" ref="A1:B10" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7DBC489E-59EF-4879-9FE4-76393ACAC418}" name="Tabell6" displayName="Tabell6" ref="A1:B10" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="A1:B10" xr:uid="{7DBC489E-59EF-4879-9FE4-76393ACAC418}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B10">
     <sortCondition ref="A1:A10"/>
@@ -1683,7 +1683,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3CAE563-162D-4C3A-BEDE-177DC1706CEB}" name="Tabell1" displayName="Tabell1" ref="A1:B4" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3CAE563-162D-4C3A-BEDE-177DC1706CEB}" name="Tabell1" displayName="Tabell1" ref="A1:B4" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
   <autoFilter ref="A1:B4" xr:uid="{A3CAE563-162D-4C3A-BEDE-177DC1706CEB}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{35D6F108-6881-4EB0-9336-2AB6B9CC07A8}" name="Prod.no"/>
@@ -1694,7 +1694,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AD8EAC2D-367A-4714-BC50-04B242895EDA}" name="Tabell4" displayName="Tabell4" ref="A1:B3" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AD8EAC2D-367A-4714-BC50-04B242895EDA}" name="Tabell4" displayName="Tabell4" ref="A1:B3" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:B3" xr:uid="{AD8EAC2D-367A-4714-BC50-04B242895EDA}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{ECAA00E3-7280-4EA3-8067-7B2E7B36DD00}" name="Prod.no"/>
